--- a/교재/엑셀교재v2/031_혼합차트_실습.xlsx
+++ b/교재/엑셀교재v2/031_혼합차트_실습.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FORYOUCOM\Documents\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD8E5E8-BF9E-47D3-9D94-3090F1BF1C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DD329F-ACB0-4454-9E5E-4B90417E0E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용안내" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>031 혼합 차트 사용 안내</t>
   </si>
@@ -114,13 +114,34 @@
   <si>
     <t>판매현황표</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>① ‘단가’ 계열이 그림과 같이 차트에 표시되도록 설정하고, ‘단가’ 계열의 차트 종류를 ‘표식이 있는 꺾은선형’으로 변경한 후, ‘보조 축’으로 지정하시오.</t>
+  </si>
+  <si>
+    <t>② 차트 제목은 [A1] 셀과 연동해서 표시되도록 하고, 글꼴은 ‘돋움’, 글꼴 스타일은 ‘굵게’, 글꼴 크기는 ‘20’으로 지정하시오.</t>
+  </si>
+  <si>
+    <t>③ 미국 ‘수량’ 계열에 데이터 레이블을 ‘값’으로 표시되도록 설정하시오.</t>
+  </si>
+  <si>
+    <t>④ 세로(값)축을 ‘최대값: 30, 기본 단위: 10’으로 설정하고, 보조 세로(값)축의 표시 형식을 ‘숫자’로 지정하고, 세로(값) 주 눈금선의 ‘선(대시 종류)’을 ‘파선’으로 하시오.</t>
+  </si>
+  <si>
+    <t>⑤ 범례를 ‘위쪽’에 표시하고, [도형 스타일]-[미세 효과 - 바다색, 강조 5]를 지정하시오.</t>
+  </si>
+  <si>
+    <t>⑥ 차트 영역의 채우기는 질감 채우기 항목 중 ‘신문 용지’로 지정하시오.</t>
+  </si>
+  <si>
+    <t>⑦ 차트 영역의 테두리 스타일은 ‘둥근 모서리’, 그림자는 바깥쪽 ‘오프셋 아래쪽’으로 지정하시오.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -154,6 +175,12 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -181,17 +208,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -215,7 +245,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
@@ -270,6 +300,41 @@
             </a:solidFill>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-AC04-4FC1-9FD0-6C0DA3C94C36}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>차트_실습!$A$4:$A$10</c:f>
@@ -397,6 +462,15 @@
       </c:ext>
     </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -777,6 +851,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1384221440"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1143,12 +1218,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="1"/>
@@ -1157,111 +1232,116 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
@@ -1271,11 +1351,6 @@
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1287,18 +1362,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:14" ht="24.95" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -1306,7 +1381,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="24.95" customHeight="1">
+    <row r="2" spans="1:14" ht="24.95" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1316,8 +1391,11 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" ht="24.95" customHeight="1">
+      <c r="N2" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="24.95" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1328,15 +1406,16 @@
         <v>17</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" ht="24.95" customHeight="1">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="N3" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="24.95" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,13 +1426,16 @@
         <v>400</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:9" ht="24.95" customHeight="1">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="N4" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="24.95" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1369,8 +1451,11 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="24.95" customHeight="1">
+      <c r="N5" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="24.95" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1381,15 +1466,16 @@
         <v>600</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" ht="24.95" customHeight="1">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="N6" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="24.95" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -1400,13 +1486,16 @@
         <v>1000</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" ht="24.95" customHeight="1">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="N7" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="24.95" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1511,11 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" ht="24.95" customHeight="1">
+      <c r="N8" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="24.95" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1434,15 +1526,13 @@
         <v>600</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" ht="24.95" customHeight="1">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:14" ht="24.95" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1453,13 +1543,13 @@
         <v>350</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" ht="24.95" customHeight="1">
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:14" ht="24.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1470,7 +1560,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="24.95" customHeight="1">
+    <row r="12" spans="1:14" ht="24.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1481,7 +1571,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="24.95" customHeight="1">
+    <row r="13" spans="1:14" ht="24.95" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1492,7 +1582,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="24.95" customHeight="1">
+    <row r="14" spans="1:14" ht="24.95" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1503,7 +1593,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" ht="24.95" customHeight="1">
+    <row r="15" spans="1:14" ht="24.95" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1514,7 +1604,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="24.95" customHeight="1">
+    <row r="16" spans="1:14" ht="24.95" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1705,11 +1795,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -1739,13 +1829,13 @@
         <v>17</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" ht="24.95" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1758,11 +1848,11 @@
         <v>400</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="24.95" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -1792,13 +1882,13 @@
         <v>600</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="24.95" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -1811,11 +1901,11 @@
         <v>1000</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="24.95" customHeight="1">
       <c r="A8" s="1" t="s">
@@ -1845,13 +1935,13 @@
         <v>600</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="24.95" customHeight="1">
       <c r="A10" s="1" t="s">
@@ -1864,11 +1954,11 @@
         <v>350</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="24.95" customHeight="1">
       <c r="A11" s="1"/>
